--- a/assets/constructions/examples/ctd_tthe_holder.xlsx
+++ b/assets/constructions/examples/ctd_tthe_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +624,26 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -633,19 +653,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AL25-5U</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AL25</t>
-        </is>
-      </c>
+          <t>ALCN25-4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>N</t>
@@ -657,7 +669,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
@@ -669,11 +681,7 @@
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>VAR_IC5/8U</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>VARGUS</t>
@@ -687,15 +695,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>VARGUS_5/8UER</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
+          <t>VARGUS_1/2ER</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>R</t>
@@ -709,10 +713,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
         <v>25</v>
@@ -725,16 +729,14 @@
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>179.1</v>
+        <v>155</v>
       </c>
       <c r="AD2" t="n">
-        <v>40</v>
+        <v>30.2</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
@@ -744,25 +746,43 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2018/VARGUS Catalog VARDEX</t>
-        </is>
+          <t>2022/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>182.55</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>16782.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SEL1212F16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>AL40-4Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>AL40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -776,7 +796,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
@@ -790,37 +810,39 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>LIKON_16EL</t>
+          <t>VAR_1/2Z</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>16ER/L</t>
-        </is>
-      </c>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ISO_5610:12X12</t>
+          <t>ISO_5610:40X40</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>LIKON_16EL</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+          <t>VARGUS_1/2ER_ZPLUS</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="b">
         <v>0</v>
@@ -832,26 +854,26 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>80</v>
+        <v>208.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
@@ -861,8 +883,22 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
+          <t>2018/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>201</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>18478.67</v>
       </c>
     </row>
     <row r="4">
@@ -873,7 +909,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AL12-3DT</t>
+          <t>OV10-2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -883,7 +919,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AL12</t>
+          <t>OV10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -901,7 +937,7 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -909,7 +945,11 @@
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VAR_IC1/4</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>VARGUS</t>
@@ -918,12 +958,12 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ISO_5610:12X12</t>
+          <t>ISO_5610:10X10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>VARGUS_3/8ERDT</t>
+          <t>VARGUS_1/4ER</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -951,21 +991,19 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>20.7</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -980,8 +1018,22 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2022 / Full MAIN VARDEX 2022-METRIC.pdf</t>
-        </is>
+          <t>2018/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7486.16</v>
       </c>
     </row>
     <row r="5">
@@ -992,7 +1044,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>STCN L 3225 P22</t>
+          <t>STCN L 2525 M22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -1029,7 +1081,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ISO_5610:32X25</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,14 +1117,14 @@
         <v>25</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA5" t="n">
         <v>32</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AD5" t="n">
         <v>32</v>
@@ -1092,20 +1144,42 @@
           <t>2022/ palbit основной каталог.pdf</t>
         </is>
       </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>210.74</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>19374.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STCN R 2525 M22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>AL20-3X</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AL20</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>N</t>
@@ -1117,7 +1191,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
@@ -1127,23 +1201,27 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>TNMC/TPMC 22..</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>VAR_IC3/8</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:20X20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PALB_TN22|PALB_TP22</t>
+          <t>VARGUS_3/8ER</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1171,24 +1249,26 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>150</v>
+        <v>128.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
@@ -1198,8 +1278,22 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2022/ palbit основной каталог.pdf</t>
-        </is>
+          <t>2018/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7987.2</v>
       </c>
     </row>
   </sheetData>
